--- a/docs/v/SAM-daily-latest.xlsx
+++ b/docs/v/SAM-daily-latest.xlsx
@@ -32332,7 +32332,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14_130603</t>
+          <t>2026-09-14_131522</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
